--- a/artfynd/A 18253-2026 artfynd.xlsx
+++ b/artfynd/A 18253-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92844675</v>
+        <v>92844667</v>
       </c>
       <c r="B2" t="n">
-        <v>101752</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 155339L</t>
+          <t>Gst Fyndnr 155347L</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92844667</v>
+        <v>92844675</v>
       </c>
       <c r="B3" t="n">
-        <v>98693</v>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 155347L</t>
+          <t>Gst Fyndnr 155339L</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>92844677</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
